--- a/MASTER DRAFT .xlsx
+++ b/MASTER DRAFT .xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C980B-588C-47EA-B7F3-1DE75E065E2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C980B-588C-47EA-B7F3-1DE75E065E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QUOTE FORMATE" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1565,12 +1576,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1592,53 +1603,29 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1683,6 +1670,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1753,7 +1746,55 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1776,56 +1817,14 @@
     <xf numFmtId="164" fontId="18" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1869,16 +1868,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1902,14 +1892,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2479,152 +2463,152 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="30.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6" ht="72" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="65" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="52"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="52"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" ht="107.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="57"/>
-    </row>
-    <row r="9" spans="1:6" s="30" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A9" s="41" t="s">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="51"/>
+    </row>
+    <row r="9" spans="1:6" s="22" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A9" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A11" s="13"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+    </row>
+    <row r="11" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A12" s="16"/>
+    <row r="12" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A12" s="4"/>
       <c r="B12" s="6"/>
       <c r="C12" s="4"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
+    <row r="13" spans="1:6" ht="24.9" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2632,15 +2616,15 @@
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="16"/>
+    <row r="14" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A14" s="4"/>
       <c r="B14" s="6"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
+    <row r="15" spans="1:6" ht="24.9" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2648,7 +2632,7 @@
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
+    <row r="16" spans="1:6" ht="24.9" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2656,7 +2640,7 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
+    <row r="17" spans="1:6" ht="24.9" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2664,7 +2648,7 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1">
+    <row r="18" spans="1:6" ht="24.9" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2672,75 +2656,70 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
     </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+    <row r="19" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="34"/>
-    </row>
-    <row r="21" spans="1:6" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="50" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="26"/>
+    </row>
+    <row r="21" spans="1:6" ht="39.9" customHeight="1">
+      <c r="A21" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="64" t="s">
+      <c r="B21" s="44"/>
+      <c r="C21" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="23" t="s">
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="39.950000000000003" customHeight="1">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="58" t="s">
+    <row r="22" spans="1:6" ht="39.9" customHeight="1">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-    </row>
-    <row r="23" spans="1:6" ht="39.950000000000003" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53" t="s">
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
+    </row>
+    <row r="23" spans="1:6" ht="39.9" customHeight="1">
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
     </row>
     <row r="24" spans="1:6" ht="102.75" customHeight="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53" t="s">
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C6:F7"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="C22:F22"/>
@@ -2753,6 +2732,11 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C6:F7"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2767,278 +2751,276 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="2" width="30.6640625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6" ht="72" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="90" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="52"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" ht="112.5" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="52" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="53" t="s">
+      <c r="D6" s="59"/>
+      <c r="E6" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" ht="30">
-      <c r="A7" s="11" t="s">
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:6" ht="28.8">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="79" t="s">
+      <c r="D7" s="46"/>
+      <c r="E7" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="79"/>
+      <c r="F7" s="67"/>
     </row>
     <row r="8" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="12" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="33" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A12" s="118"/>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
-    </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A13" s="118"/>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="118"/>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-    </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A15" s="118"/>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A16" s="118"/>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A17" s="118"/>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A18" s="118"/>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
+    <row r="12" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+    </row>
+    <row r="13" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+    </row>
+    <row r="14" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+    </row>
+    <row r="16" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
     </row>
     <row r="19" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="71" t="s">
+      <c r="B19" s="69"/>
+      <c r="C19" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="37"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="29"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
     </row>
     <row r="21" spans="1:6" ht="51.75" customHeight="1">
-      <c r="A21" s="69"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="77" t="s">
+      <c r="A21" s="79"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="11" t="s">
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="58" t="s">
+      <c r="B22" s="74"/>
+      <c r="C22" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
     </row>
     <row r="23" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="53" t="s">
+      <c r="A23" s="75"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
     </row>
     <row r="24" spans="1:6" ht="86.25" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="53" t="s">
+      <c r="B24" s="78"/>
+      <c r="C24" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="A8:F8"/>
@@ -3051,11 +3033,13 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A22:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="79" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
@@ -3069,138 +3053,138 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="46.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="46.5" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="2" width="30.6640625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="65" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="52"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="52"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" ht="120" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="52" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="53" t="s">
+      <c r="D6" s="59"/>
+      <c r="E6" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="53"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-    </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="64"/>
+    </row>
+    <row r="9" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="12" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30.75" customHeight="1">
       <c r="A10" s="4"/>
-      <c r="B10" s="12"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="4"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
+    <row r="11" spans="1:6" ht="24.9" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3208,7 +3192,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
+    <row r="12" spans="1:6" ht="24.9" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="6"/>
       <c r="C12" s="4"/>
@@ -3216,7 +3200,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
+    <row r="13" spans="1:6" ht="24.9" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3224,135 +3208,118 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="93" t="s">
+    <row r="14" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A14" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A15" s="95"/>
-      <c r="B15" s="96"/>
+    <row r="15" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A16" s="95"/>
-      <c r="B16" s="96"/>
+    <row r="16" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A16" s="91"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A17" s="95"/>
-      <c r="B17" s="96"/>
+    <row r="17" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="98"/>
+    <row r="18" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="72" t="s">
+      <c r="B19" s="69"/>
+      <c r="C19" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="37"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="29"/>
     </row>
     <row r="20" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
     </row>
     <row r="21" spans="1:6" ht="72" customHeight="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="100"/>
-      <c r="C21" s="105" t="s">
+      <c r="B21" s="96"/>
+      <c r="C21" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="11" t="s">
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="102"/>
-      <c r="C22" s="58" t="s">
+      <c r="A22" s="97"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="103"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="53" t="s">
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
     </row>
     <row r="24" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="53" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="A24:B24"/>
@@ -3360,595 +3327,10 @@
     <mergeCell ref="A14:B18"/>
     <mergeCell ref="A21:B23"/>
     <mergeCell ref="C19:E19"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="256" scale="81" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E100D8-CE6E-40F1-8413-A338847C2C66}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="46.5" customHeight="1"/>
-  <cols>
-    <col min="1" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A1" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="52"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="52"/>
-    </row>
-    <row r="5" spans="1:6" ht="124.5" customHeight="1">
-      <c r="A5" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-    </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-    </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-    </row>
-    <row r="18" spans="1:6" ht="21" customHeight="1">
-      <c r="A18" s="71" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="38">
-        <f>SUM(E10:E17)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="40">
-        <f>SUM(F10:F17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A19" s="82" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="84"/>
-    </row>
-    <row r="20" spans="1:6" ht="72" customHeight="1">
-      <c r="A20" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="111" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="113"/>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="114"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="60"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="87"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-    </row>
-    <row r="23" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A23" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C20:F20"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:B22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="79" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F50A3D-8B8D-48D1-9B30-CA99D8C88528}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="46.5" customHeight="1"/>
-  <cols>
-    <col min="1" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A1" s="117" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="52"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="52"/>
-    </row>
-    <row r="5" spans="1:6" ht="120" customHeight="1">
-      <c r="A5" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="52"/>
-    </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A14" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A15" s="95"/>
-      <c r="B15" s="96"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A16" s="95"/>
-      <c r="B16" s="96"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A17" s="95"/>
-      <c r="B17" s="96"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1">
-      <c r="A19" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A20" s="82" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
-    </row>
-    <row r="21" spans="1:6" ht="72" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="105" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-    </row>
-    <row r="24" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A24" s="91" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A14:B18"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:B23"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:D6"/>
@@ -3964,6 +3346,608 @@
     <mergeCell ref="E4:F4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" scale="81" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E100D8-CE6E-40F1-8413-A338847C2C66}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="46.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="30.6640625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A1" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="54"/>
+      <c r="E3" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="46"/>
+    </row>
+    <row r="4" spans="1:6" ht="30" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="46"/>
+    </row>
+    <row r="5" spans="1:6" ht="124.5" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+    </row>
+    <row r="8" spans="1:6" ht="27" customHeight="1">
+      <c r="A8" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="64"/>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" customHeight="1">
+      <c r="A9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="21" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="1:6" ht="21" customHeight="1">
+      <c r="A18" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="83"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="30">
+        <f>SUM(E10:E17)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="32">
+        <f>SUM(F10:F17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="47.25" hidden="1" customHeight="1">
+      <c r="A19" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+    </row>
+    <row r="20" spans="1:6" ht="72" customHeight="1">
+      <c r="A20" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="104" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="106"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
+      <c r="A21" s="107"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="54"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
+      <c r="A22" s="75"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+    </row>
+    <row r="23" spans="1:6" ht="66.75" customHeight="1">
+      <c r="A23" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="103"/>
+      <c r="C23" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:B22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F50A3D-8B8D-48D1-9B30-CA99D8C88528}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="46.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="30.6640625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="32.25" customHeight="1">
+      <c r="A1" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="46"/>
+      <c r="E3" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="46"/>
+    </row>
+    <row r="4" spans="1:6" ht="30" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="46"/>
+    </row>
+    <row r="5" spans="1:6" ht="120" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="1:6" ht="27" customHeight="1">
+      <c r="A8" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="64"/>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" customHeight="1">
+      <c r="A9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A12" s="4"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A14" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="90"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A16" s="91"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.9" customHeight="1">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="21" customHeight="1">
+      <c r="A19" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="69"/>
+      <c r="C19" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="29"/>
+    </row>
+    <row r="20" spans="1:6" ht="47.25" hidden="1" customHeight="1">
+      <c r="A20" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
+    </row>
+    <row r="21" spans="1:6" ht="72" customHeight="1">
+      <c r="A21" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="47"/>
+      <c r="C21" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+    </row>
+    <row r="24" spans="1:6" ht="66.75" customHeight="1">
+      <c r="A24" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A14:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:B23"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/MASTER DRAFT .xlsx
+++ b/MASTER DRAFT .xlsx
@@ -3,20 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C980B-588C-47EA-B7F3-1DE75E065E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509EE1D8-8E06-4A76-B698-0EA12CBC1D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QUOTE FORMATE" sheetId="2" r:id="rId1"/>
-    <sheet name="Sample Invoice" sheetId="3" r:id="rId2"/>
-    <sheet name="Proforma Invoice" sheetId="4" r:id="rId3"/>
-    <sheet name="Packing List" sheetId="5" r:id="rId4"/>
-    <sheet name="Commercial Invoice" sheetId="6" r:id="rId5"/>
+    <sheet name="PO" sheetId="7" r:id="rId2"/>
+    <sheet name="Sample Invoice" sheetId="3" r:id="rId3"/>
+    <sheet name="Proforma Invoice" sheetId="4" r:id="rId4"/>
+    <sheet name="Packing List" sheetId="5" r:id="rId5"/>
+    <sheet name="Commercial Invoice" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'QUOTE FORMATE'!$A$1:$F$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Sample Invoice'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Sample Invoice'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="112">
   <si>
     <t>Price</t>
   </si>
@@ -62,9 +63,112 @@
     <t>Quotation</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Buyer Reference:
+    <t>PRODUCT DISCRIPTION</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Signatory Company:
 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VISION LIMELITE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Name Of Authorised Signatory:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VEDANT PATEL</t>
+    </r>
+  </si>
+  <si>
+    <t>Signature:</t>
+  </si>
+  <si>
+    <t>SAMPLE  INVOICE</t>
+  </si>
+  <si>
+    <t>Buyer ( If Other than Consinee ) :</t>
+  </si>
+  <si>
+    <t>Vessel / Flight No :</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount in words : USD FIVE  THOUNSAND NINE HUNDRED ONLY  </t>
+  </si>
+  <si>
+    <t>NOT FOR SALE</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Description of Goods</t>
+  </si>
+  <si>
+    <t>Rate (USD)</t>
+  </si>
+  <si>
+    <t>PROFORMA  INVOICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terms of Delivery ( Incoterms ) and Payment :
+</t>
+  </si>
+  <si>
+    <t>We declare that this Invoice shows the actual Price of goods described and that all particulars are ture and correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyer's Order No : </t>
+  </si>
+  <si>
+    <t>Net Weight</t>
+  </si>
+  <si>
+    <t>Gross Weight</t>
+  </si>
+  <si>
+    <t>Bag / Carton Per KGs</t>
+  </si>
+  <si>
+    <t>COMMERCIAL  INVOICE</t>
+  </si>
+  <si>
+    <t>Container No :</t>
+  </si>
+  <si>
+    <t>Rate (USD) per kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                            </t>
+  </si>
+  <si>
+    <t>Packing List</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Buyer ( If Other than Consinee ) : </t>
     </r>
     <r>
       <rPr>
@@ -75,15 +179,157 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Online</t>
-    </r>
-  </si>
-  <si>
-    <t>PRODUCT DISCRIPTION</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Signatory Company:
+      <t>N.A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Buyer ( If Other than Consinee ) : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.A.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">HS Code </t>
+  </si>
+  <si>
+    <t>Unit Rate (USD)</t>
+  </si>
+  <si>
+    <t>The goods are non-hazardous and comply with export regulations.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Purpose: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Free Sample – No Commercial Value – For Testing Only</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> No. of Packages</t>
+  </si>
+  <si>
+    <t>We hereby confirm that the above packing list corresponds to the commercial invoice and contains psyllium husk and psyllium powder samples intended only for testing purposes, with no commercial value.</t>
+  </si>
+  <si>
+    <t>NON-HAZARDOUS FOOD SAMPLE</t>
+  </si>
+  <si>
+    <t>We hereby declare that the above-mentioned goods are free samples of psyllium husk and psyllium powder, supplied without any commercial value and intended only for laboratory testing and evaluation purposes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IEC No:                                                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DUBPP8360J</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IEC No:                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DUBPP8360J</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IEC No:                                             </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DUBPP8360J</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">IEC No:                                            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DUBPP8360J</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exporter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -97,11 +343,17 @@
       </rPr>
       <t>VISION LIMELITE</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Name Of Authorised Signatory:
-</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
+Business Hub, Ranip, Ahmedabad, Gujarat 380004 - </t>
     </r>
     <r>
       <rPr>
@@ -112,17 +364,210 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>VEDANT PATEL</t>
-    </r>
-  </si>
-  <si>
-    <t>Signature:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Port Of Loading :
+      <t xml:space="preserve">INDIA
 </t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GST : 24DUBPP8360J1ZB
+(+91) 83476 72514 - Vedant Patel
+info@seabridgeexports.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Vessel / Flight No : -</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exporter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VISION LIMELITE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
+Business Hub, Ranip, Ahmedabad, Gujarat 382480 - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">INDIA
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GST : 24DUBPP8360J1ZB
+(+91) 83476 72514 - Vedant Patel
+info@seabridgeexports.com</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Seller
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VISION LIMELITE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
+Business Hub, Ranip, Ahmedabad, Gujarat 382480. - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">INDIA
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IEC - DUBPP8360J
+(+91) 96385 18686 - Vedant Patel
+info@seabridgeexports.com</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice Date :                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice No:
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Consignee</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                              </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                    </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Of Discharge:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type Of Shipment:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathod Of Dispatch:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Origin of Goods:            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Final Destination:           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency:
+</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -132,13 +577,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Ahmedabad</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Port Of Discharge:
-</t>
+      <t>Net Weight</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :            </t>
     </r>
     <r>
       <rPr>
@@ -149,76 +598,37 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Genoa</t>
-    </r>
-  </si>
-  <si>
-    <t>SAMPLE  INVOICE</t>
-  </si>
-  <si>
-    <t>Buyer ( If Other than Consinee ) :</t>
-  </si>
-  <si>
-    <t>Vessel / Flight No :</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount in words : USD FIVE  THOUNSAND NINE HUNDRED ONLY  </t>
-  </si>
-  <si>
-    <t>NOT FOR SALE</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Description of Goods</t>
-  </si>
-  <si>
-    <t>Rate (USD)</t>
-  </si>
-  <si>
-    <t>PROFORMA  INVOICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terms of Delivery ( Incoterms ) and Payment :
+      <t xml:space="preserve">                                                                                      Gross Weight :            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                </t>
+    </r>
+  </si>
+  <si>
+    <t>Amount in words :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incoterms:
 </t>
   </si>
   <si>
-    <t>We declare that this Invoice shows the actual Price of goods described and that all particulars are ture and correct.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buyer's Order No : </t>
-  </si>
-  <si>
-    <t>Net Weight</t>
-  </si>
-  <si>
-    <t>Gross Weight</t>
-  </si>
-  <si>
-    <t>Bag / Carton Per KGs</t>
-  </si>
-  <si>
-    <t>COMMERCIAL  INVOICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Cartons / Box :       20  BOXS                                                                                                                                                                                                                                                               Net Weight :                      1.5 KGS                                                                        Gross Weight :                     2  KGS                                                                           </t>
-  </si>
-  <si>
-    <t>Container No :</t>
-  </si>
-  <si>
-    <t>Rate (USD) per kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                            </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Country of Origin of Goods:                 </t>
+    <t xml:space="preserve">Port Of Loading :
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terms / Mathod Of Payment
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Buyer</t>
     </r>
     <r>
       <rPr>
@@ -228,525 +638,15 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>India</t>
-    </r>
-  </si>
-  <si>
-    <t>Packing List</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Buyer ( If Other than Consinee ) : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N.A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mathod Of Dispatch:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve">                                                                                                              </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Air</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Buyer ( If Other than Consinee ) : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N.A.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">HS Code </t>
-  </si>
-  <si>
-    <t>Unit Rate (USD)</t>
-  </si>
-  <si>
-    <t>The goods are non-hazardous and comply with export regulations.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Type Of Shipment:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sample Shipment</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Free Sample – No Commercial Value – For Testing Only</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> No. of Packages</t>
-  </si>
-  <si>
-    <t>We hereby confirm that the above packing list corresponds to the commercial invoice and contains psyllium husk and psyllium powder samples intended only for testing purposes, with no commercial value.</t>
-  </si>
-  <si>
-    <t>NON-HAZARDOUS FOOD SAMPLE</t>
-  </si>
-  <si>
-    <t>We hereby declare that the above-mentioned goods are free samples of psyllium husk and psyllium powder, supplied without any commercial value and intended only for laboratory testing and evaluation purposes.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IEC No:                                                   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DUBPP8360J</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IEC No:                                                               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DUBPP8360J</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IEC No:                                             </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DUBPP8360J</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IEC No:                                            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DUBPP8360J</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Exporter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VISION LIMELITE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
-Business Hub, Ranip, Ahmedabad, Gujarat 380004 - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">INDIA
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GST : 24DUBPP8360J1ZB
-(+91) 83476 72514 - Vedant Patel
-info@seabridgeexports.com</t>
-    </r>
-  </si>
-  <si>
-    <t>Vessel / Flight No : -</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Exporter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VISION LIMELITE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
-Business Hub, Ranip, Ahmedabad, Gujarat 382480 - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">INDIA
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GST : 24DUBPP8360J1ZB
-(+91) 83476 72514 - Vedant Patel
-info@seabridgeexports.com</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Seller
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VISION LIMELITE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
-Business Hub, Ranip, Ahmedabad, Gujarat 382480. - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">INDIA
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>IEC - DUBPP8360J
-(+91) 96385 18686 - Vedant Patel
-info@seabridgeexports.com</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice Date :                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice No:
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Consignee</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                              </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                    </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Port Of Discharge:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type Of Shipment:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathod Of Dispatch:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country of Origin of Goods:            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country of Final Destination:           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency:
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Net Weight</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> :            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                      Gross Weight :            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                </t>
-    </r>
-  </si>
-  <si>
-    <t>Amount in words :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incoterms:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port Of Loading :
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terms / Mathod Of Payment
-</t>
-  </si>
-  <si>
-    <r>
-      <t>Buyer</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                              </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">                          </t>
     </r>
   </si>
@@ -761,45 +661,6 @@
   <si>
     <t xml:space="preserve">Expiry: 
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Prices quoted are on Basis as per Incoterms
-• Goods supplied shall comply with the applicable food safety regulations of the UAE and relevant international food safety standards.
-• Inspection will be conducted at seller’s premises. Third-party inspection if required will be borne by buyer.
-• Seller shall not be liable for delay or non-performance due to circumstances beyond control such as natural calamities, war, strike, government restrictions, etc.
-• All disputes shall be subject to Ahmedabad (Gujarat) jurisdiction only.
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Consignee</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                              MartinoRossi SpA                                                                                                      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                    </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Country of Origin of Goods:              </t>
@@ -937,6 +798,183 @@
       </rPr>
       <t>ALL BANKING CHARGES OUTSIDE INDIA ARE  IN ACCOUNT OF APPLICANT</t>
     </r>
+  </si>
+  <si>
+    <t>Total Cartons / Box : 
+Net Weight :                                                                                             
+Gross Weight :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount in words : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Origin of Goods:                 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Consignee</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                                                                                                                              </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                    </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyer Reference:
+</t>
+  </si>
+  <si>
+    <t>• Prices quoted are on Basis as per Incoterms
+• Goods supplied shall comply with the applicable food safety regulations as per country relevant international food safety standards.
+• Inspection will be conducted at seller’s premises. Third-party inspection if required will be borne by buyer.
+• Seller shall not be liable for delay or non-performance due to circumstances beyond control such as natural calamities, war, strike, government restrictions, etc.</t>
+  </si>
+  <si>
+    <t>PURCHASE ORDER</t>
+  </si>
+  <si>
+    <t>Purchaser (Buyer)
+VISION LIMELITE
+BH-815, 8th Floor Arved transcube plaza, Opp. Metro Station
+Business Hub, Ranip, Ahmedabad, Gujarat 380004 - INDIA
+GST : 24DUBPP8360J1ZB
+IEC : DUBPP8360J
+(+91) 83476 72514 - Vedant Patel
+info@seabridgeexports.com</t>
+  </si>
+  <si>
+    <t>PO Number:
+[VL/PO/26-XXXX]</t>
+  </si>
+  <si>
+    <t>Date:
+[DD Month YYYY]</t>
+  </si>
+  <si>
+    <t>Supplier Ref / Quotation No:
+[Supplier quote ref, if any]</t>
+  </si>
+  <si>
+    <t>Expected Delivery Date:
+[DD Month YYYY]</t>
+  </si>
+  <si>
+    <t>Supplier / Vendor
+[Supplier / Factory Name]
+[Factory Address]
+[Unjha / Deesa, Gujarat - INDIA]
+[GST No, if available]
+[Contact Person Name]
+[Phone Number]
+[Email Address]</t>
+  </si>
+  <si>
+    <t>Delivery / Consignment Address (if different from Purchaser):
+[Warehouse / Port / Processing unit address, if goods are to be
+delivered directly to a third location such as Mundra Port]</t>
+  </si>
+  <si>
+    <t>Mode of Delivery:
+[Road / Ex-Factory Pickup]</t>
+  </si>
+  <si>
+    <t>Expected Mode of Payment:
+[e.g. 50% Advance, 50% on Delivery]</t>
+  </si>
+  <si>
+    <t>Order Currency:
+INR</t>
+  </si>
+  <si>
+    <t>Delivery / Pickup Location:
+[Factory Unjha / Deesa]</t>
+  </si>
+  <si>
+    <t>Destination:
+[Sea Bridge Exports Warehouse / Mundra Port ICD]</t>
+  </si>
+  <si>
+    <t>Required By:
+[DD Month YYYY]</t>
+  </si>
+  <si>
+    <t>PRODUCT / MATERIAL ORDERED</t>
+  </si>
+  <si>
+    <t>Product Code</t>
+  </si>
+  <si>
+    <t>Rate (INR)</t>
+  </si>
+  <si>
+    <t>Psyllium Husk / Husk Powder — [purity / mesh spec]</t>
+  </si>
+  <si>
+    <t>[qty]</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>[rate]</t>
+  </si>
+  <si>
+    <t>Packing Instructions:  [e.g. 25kg HDPE bags with inner liner]
+Quality Requirement:  Batch-wise COA required with delivery
+(purity, swelling index, moisture, microbial parameters)
+Variation % +/- :   [e.g. 5%]</t>
+  </si>
+  <si>
+    <t>Terms &amp; Conditions:  
+• This Purchase Order is issued subject to the supplier confirming the above quantity, rate, and delivery date in writing.  
+• Goods must be accompanied by a batch-wise Certificate of Analysis (COA) at the time of delivery.  
+• Any change in quantity, specification, or price must be approved in writing by Vision Limelite before dispatch.  
+• Supplier is responsible for quality and packaging until goods are received and inspected at the destination noted above.  
+• Payment will be released as per the terms agreed above, subject to quality acceptance.  
+• All disputes shall be subject to Ahmedabad (Gujarat) jurisdiction only.</t>
+  </si>
+  <si>
+    <t>Terms of Delivery and Payment :
+[e.g. Ex-Factory Unjha, 50% advance on PO confirmation,
+50% on delivery against COA]</t>
+  </si>
+  <si>
+    <t>Currency:
+INR</t>
+  </si>
+  <si>
+    <t>Signatory Company:
+VISION LIMELITE</t>
+  </si>
+  <si>
+    <t>Name Of Authorised Signatory:
+VEDANT PATEL
+Signature:</t>
+  </si>
+  <si>
+    <t>This Purchase Order is issued in good faith based on the specifications and pricing discussed. It becomes binding once acknowledged by the Supplier.</t>
   </si>
 </sst>
 </file>
@@ -947,7 +985,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +1149,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1152,7 +1220,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1563,6 +1631,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1576,7 +1653,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1673,6 +1750,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1694,57 +1890,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1770,126 +1915,150 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="30" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="31" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="31" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="28" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="29" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="7" borderId="30" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="31" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="28" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="29" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1981,6 +2150,54 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1013460</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B3D2893-B8B2-41FA-B920-519A80CC78F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3543300" y="381000"/>
+          <a:ext cx="3870960" cy="784860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>225137</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>147205</xdr:rowOff>
@@ -2031,7 +2248,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2086,7 +2303,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2141,7 +2358,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2475,101 +2692,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6" ht="72" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="A2" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
     </row>
     <row r="3" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="46"/>
-    </row>
-    <row r="4" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" spans="1:6" ht="107.25" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" customHeight="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="149.4" customHeight="1">
+      <c r="A5" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
+        <v>53</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A8" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="51"/>
+      <c r="A8" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="66"/>
     </row>
     <row r="9" spans="1:6" s="22" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>2</v>
@@ -2665,61 +2882,63 @@
       <c r="F19" s="28"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="57"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="72"/>
       <c r="F20" s="26"/>
     </row>
     <row r="21" spans="1:6" ht="39.9" customHeight="1">
-      <c r="A21" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
+      <c r="A21" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="16" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="39.9" customHeight="1">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="52" t="s">
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="69"/>
+    </row>
+    <row r="23" spans="1:6" ht="39.9" customHeight="1">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54"/>
-    </row>
-    <row r="23" spans="1:6" ht="39.9" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47" t="s">
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+    </row>
+    <row r="24" spans="1:6" ht="102.75" customHeight="1">
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-    </row>
-    <row r="24" spans="1:6" ht="102.75" customHeight="1">
-      <c r="A24" s="47"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="C22:F22"/>
@@ -2731,12 +2950,9 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C6:F7"/>
-    <mergeCell ref="C5:F5"/>
     <mergeCell ref="A2:B4"/>
-    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2746,6 +2962,301 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534039F9-25C0-4B11-9C52-F2A41D8298E1}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="31.2">
+      <c r="A1" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1">
+      <c r="A2" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="54"/>
+    </row>
+    <row r="4" spans="1:6" ht="52.2" customHeight="1">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="54"/>
+    </row>
+    <row r="5" spans="1:6" ht="121.2" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="54"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
+      <c r="A6" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="54"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1">
+      <c r="A7" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="54"/>
+    </row>
+    <row r="8" spans="1:6" ht="18">
+      <c r="A8" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="44"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="43.2">
+      <c r="A10" s="38">
+        <v>12119032</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" ref="F10:F13" si="0">IF(AND(ISNUMBER(C10),ISNUMBER(E10)),C10*E10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A14" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.2" customHeight="1">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
+    </row>
+    <row r="17" spans="1:6" ht="21" customHeight="1">
+      <c r="A17" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="38"/>
+    </row>
+    <row r="18" spans="1:6" ht="28.8">
+      <c r="A18" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1">
+      <c r="A19" s="45"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+    </row>
+    <row r="20" spans="1:6" ht="118.8" customHeight="1">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
+    </row>
+    <row r="21" spans="1:6" ht="33" customHeight="1">
+      <c r="A21" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A14:F16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DC0517-2A18-45F3-879A-934458E5AD15}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2759,116 +3270,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A1" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="A1" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6" ht="72" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="A2" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="46"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" spans="1:6" ht="112.5" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="47.4" customHeight="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="148.19999999999999" customHeight="1">
+      <c r="A5" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="47"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="67"/>
+        <v>53</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="59"/>
+      <c r="E7" s="91" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="91"/>
     </row>
     <row r="8" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A8" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
+      <c r="A8" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="88"/>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>3</v>
@@ -2946,73 +3457,73 @@
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
     </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A19" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="83"/>
+    <row r="19" spans="1:6" ht="26.4" customHeight="1">
+      <c r="A19" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="93"/>
+      <c r="C19" s="105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="106"/>
+      <c r="E19" s="107"/>
       <c r="F19" s="29"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A20" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
-    </row>
-    <row r="21" spans="1:6" ht="51.75" customHeight="1">
-      <c r="A21" s="79"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
+      <c r="A20" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+    </row>
+    <row r="21" spans="1:6" ht="70.2" customHeight="1">
+      <c r="A21" s="103"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
       <c r="F21" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A22" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="41.4" customHeight="1">
+      <c r="A22" s="97" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="98"/>
+      <c r="C22" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="69"/>
+    </row>
+    <row r="23" spans="1:6" ht="45" customHeight="1">
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54"/>
-    </row>
-    <row r="23" spans="1:6" ht="30.75" customHeight="1">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="47" t="s">
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+    </row>
+    <row r="24" spans="1:6" ht="86.25" customHeight="1">
+      <c r="A24" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="102"/>
+      <c r="C24" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-    </row>
-    <row r="24" spans="1:6" ht="86.25" customHeight="1">
-      <c r="A24" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="78"/>
-      <c r="C24" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3047,7 +3558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F310A8-8116-4C71-8DBD-1257C057CD2D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3061,116 +3572,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="63" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+    </row>
+    <row r="2" spans="1:6" ht="60" customHeight="1">
+      <c r="A2" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="47.4" customHeight="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-    </row>
-    <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="46"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" spans="1:6" ht="120" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="148.80000000000001" customHeight="1">
+      <c r="A5" s="76" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="47"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
+        <v>53</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="59"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
+      <c r="A8" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="88"/>
     </row>
     <row r="9" spans="1:6" ht="24.9" customHeight="1">
       <c r="A9" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>3</v>
@@ -3209,114 +3720,114 @@
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A14" s="89" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="90"/>
+      <c r="A14" s="115" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="116"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
+      <c r="A15" s="117"/>
+      <c r="B15" s="118"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92"/>
+      <c r="A16" s="117"/>
+      <c r="B16" s="118"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
+      <c r="A17" s="117"/>
+      <c r="B17" s="118"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
+      <c r="A18" s="119"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1">
-      <c r="A19" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
+      <c r="A19" s="108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="109"/>
+      <c r="C19" s="127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
       <c r="F19" s="29"/>
     </row>
     <row r="20" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A20" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
+      <c r="A20" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
     </row>
     <row r="21" spans="1:6" ht="72" customHeight="1">
-      <c r="A21" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
+      <c r="A21" s="121" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="122"/>
+      <c r="C21" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
       <c r="F21" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="52" t="s">
+      <c r="A22" s="123"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="69"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
+      <c r="A23" s="125"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="47" t="s">
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+    </row>
+    <row r="24" spans="1:6" ht="66.75" customHeight="1">
+      <c r="A24" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="114"/>
+      <c r="C24" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-    </row>
-    <row r="24" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3351,7 +3862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E100D8-CE6E-40F1-8413-A338847C2C66}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3365,119 +3876,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A1" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
+      <c r="A1" s="128" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="A2" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="46"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" spans="1:6" ht="124.5" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="69"/>
+      <c r="E3" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="48" customHeight="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="149.4" customHeight="1">
+      <c r="A5" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="47"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
+      <c r="A8" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="88"/>
     </row>
     <row r="9" spans="1:6" ht="30.75" customHeight="1">
       <c r="A9" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1">
@@ -3506,7 +4017,7 @@
     </row>
     <row r="13" spans="1:6" ht="24.9" customHeight="1">
       <c r="A13" s="19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="17"/>
@@ -3547,10 +4058,10 @@
       <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" ht="21" customHeight="1">
-      <c r="A18" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="83"/>
+      <c r="A18" s="134" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="135"/>
       <c r="C18" s="30"/>
       <c r="D18" s="31"/>
       <c r="E18" s="30">
@@ -3563,58 +4074,58 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A19" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
+      <c r="A19" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
     </row>
     <row r="20" spans="1:6" ht="72" customHeight="1">
-      <c r="A20" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="74"/>
-      <c r="C20" s="104" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="106"/>
+      <c r="A20" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="98"/>
+      <c r="C20" s="131" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="133"/>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="107"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="52" t="s">
+      <c r="A21" s="136"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="69"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="54"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="75"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="47" t="s">
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+    </row>
+    <row r="23" spans="1:6" ht="66.75" customHeight="1">
+      <c r="A23" s="129" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="130"/>
+      <c r="C23" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-    </row>
-    <row r="23" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A23" s="102" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="103"/>
-      <c r="C23" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -3647,12 +4158,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F50A3D-8B8D-48D1-9B30-CA99D8C88528}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="46.5" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="30.6640625" style="1" customWidth="1"/>
@@ -3661,118 +4172,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A1" s="109" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
+      <c r="A1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="A2" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="46"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="46"/>
-    </row>
-    <row r="5" spans="1:6" ht="120" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="54" customHeight="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="155.4" customHeight="1">
+      <c r="A5" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="47"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="46"/>
+        <v>53</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="59"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
-      <c r="A8" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="64"/>
+      <c r="A8" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="88"/>
     </row>
     <row r="9" spans="1:6" ht="30.75" customHeight="1">
       <c r="A9" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>3</v>
@@ -3811,114 +4322,98 @@
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A14" s="89" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="98"/>
     </row>
     <row r="15" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="136"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="137"/>
     </row>
     <row r="16" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.9" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1">
-      <c r="A19" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="29"/>
-    </row>
-    <row r="20" spans="1:6" ht="47.25" hidden="1" customHeight="1">
-      <c r="A20" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
-    </row>
-    <row r="21" spans="1:6" ht="72" customHeight="1">
-      <c r="A21" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="52" t="s">
+      <c r="A16" s="99"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="100"/>
+    </row>
+    <row r="17" spans="1:6" ht="21" customHeight="1">
+      <c r="A17" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="93"/>
+      <c r="C17" s="127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="29"/>
+    </row>
+    <row r="18" spans="1:6" ht="47.25" hidden="1" customHeight="1">
+      <c r="A18" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="96"/>
+    </row>
+    <row r="19" spans="1:6" ht="72" customHeight="1">
+      <c r="A19" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47" t="s">
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+    </row>
+    <row r="22" spans="1:6" ht="66.75" customHeight="1">
+      <c r="A22" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="114"/>
+      <c r="C22" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-    </row>
-    <row r="24" spans="1:6" ht="66.75" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3935,17 +4430,17 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A14:B18"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:B21"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:B23"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="A14:F16"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
